--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104522_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104522_W8.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4431</v>
+        <v>1.7111</v>
       </c>
       <c r="E2" t="n">
-        <v>2.0579</v>
+        <v>3.1311</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6149</v>
+        <v>-1.42</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0391</v>
+        <v>0.0272</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6149</v>
+        <v>0.6037</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5758</v>
+        <v>-0.5765</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9888</v>
+        <v>2.9449</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7579</v>
+        <v>0.7337</v>
       </c>
       <c r="L2" t="n">
-        <v>2.2309</v>
+        <v>2.2112</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.9497</v>
+        <v>-2.9177</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.8066</v>
+        <v>-2.7877</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0763</v>
+        <v>-0.791</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.5303</v>
+        <v>-0.3977</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.3932</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.2652</v>
+        <v>-0.9627</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4586</v>
+        <v>-0.1646</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8067</v>
+        <v>-0.7982</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.7374</v>
+        <v>-3.7122</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0156</v>
+        <v>0.0308</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.753</v>
+        <v>-3.743</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5986</v>
+        <v>-0.6077</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1905</v>
+        <v>0.1896</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7891</v>
+        <v>-0.7973</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.1388</v>
+        <v>-3.1045</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.9639</v>
+        <v>-2.9457</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2064</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9527</v>
+        <v>-0.6463</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2538</v>
+        <v>-0.2887</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8639</v>
+        <v>1.8634</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="4">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.8283</v>
+        <v>-1.1222</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.1626</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3883</v>
+        <v>-2.2848</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.5851</v>
+        <v>-2.5953</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6042</v>
+        <v>-1.6245</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5805</v>
+        <v>0.5369</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.6184</v>
+        <v>-1.6525</v>
       </c>
       <c r="L4" t="n">
-        <v>2.199</v>
+        <v>2.1893</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.1656</v>
+        <v>-3.1321</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.1798</v>
+        <v>-3.1601</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4947</v>
+        <v>-0.7758</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3912</v>
+        <v>-0.7321</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1035</v>
+        <v>-0.0436</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W4" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.0837</v>
+        <v>-1.8236</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3826</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7011</v>
+        <v>-0.8504</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.9198</v>
+        <v>-1.8852</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1313</v>
+        <v>-0.2185</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7885</v>
+        <v>-1.6667</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7317</v>
+        <v>-0.4249</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.769</v>
+        <v>0.3275</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0373</v>
+        <v>-0.7524</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.188</v>
+        <v>-1.4603</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3622</v>
+        <v>-0.546</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8258</v>
+        <v>-0.9143</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2631</v>
+        <v>-0.1661</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2299</v>
+        <v>-0.3207</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0333</v>
+        <v>0.1546</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>K. ZORIKS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0995</v>
+        <v>-2.3295</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2033</v>
+        <v>-1.2256</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8961</v>
+        <v>-1.1039</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8935</v>
+        <v>-1.3283</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2223</v>
+        <v>0.7929</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6712</v>
+        <v>-2.1212</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.42</v>
+        <v>0.0033</v>
       </c>
       <c r="K6" t="n">
-        <v>0.329</v>
+        <v>0.7929</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.749</v>
+        <v>-0.7896</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4735</v>
+        <v>-1.3315</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5513</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9222</v>
+        <v>-1.3315</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4328</v>
+        <v>-0.0907</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5565</v>
+        <v>-0.0907</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1237</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. ZORIKS</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4412</v>
+        <v>-2.4376</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3326</v>
+        <v>-0.7494</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1086</v>
+        <v>-1.6882</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3252</v>
+        <v>-2.9113</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7966</v>
+        <v>-1.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.1218</v>
+        <v>-1.7797</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0102</v>
+        <v>-0.7352</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7966</v>
+        <v>-0.7724</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7864</v>
+        <v>0.0372</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3354</v>
+        <v>-2.1761</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.3592</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3354</v>
+        <v>-1.8169</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2087</v>
+        <v>-0.1233</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.0327</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6735</v>
+        <v>-2.8037</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6511</v>
+        <v>-4.1317</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0224</v>
+        <v>1.328</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5557</v>
+        <v>-3.6805</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6047</v>
+        <v>-4.135</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9511</v>
+        <v>0.4545</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5332</v>
+        <v>-3.8388</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6825</v>
+        <v>-3.876</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1493</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0225</v>
+        <v>0.1583</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07779999999999999</v>
+        <v>-0.259</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1003</v>
+        <v>0.4173</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4788</v>
+        <v>-0.2614</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1179</v>
+        <v>-0.2929</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3608</v>
+        <v>0.0316</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1622</v>
+        <v>-3.1109</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3573</v>
+        <v>-0.8907</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.805</v>
+        <v>-2.2202</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.71</v>
+        <v>-2.5394</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3534</v>
+        <v>-0.6005</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0635</v>
+        <v>-1.9389</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8002</v>
+        <v>-0.5373</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6061</v>
+        <v>-0.6862</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1941</v>
+        <v>0.1489</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5103</v>
+        <v>-2.0022</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2526</v>
+        <v>0.0857</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2576</v>
+        <v>-2.0879</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1337</v>
+        <v>-0.9372</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1179</v>
+        <v>-0.3534</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2516</v>
+        <v>-0.5838</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7712</v>
+        <v>-0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5575</v>
+        <v>-3.2186</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.6497</v>
+        <v>-1.3719</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0922</v>
+        <v>-1.8467</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.6703</v>
+        <v>-0.6955</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.1209</v>
+        <v>0.3587</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4505</v>
+        <v>-1.0542</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.815</v>
+        <v>1.7949</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.8523</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>1.1916</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1446</v>
+        <v>-2.4904</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2685</v>
+        <v>-0.2446</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4132</v>
+        <v>-2.2458</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0213</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8347</v>
+        <v>-0.1165</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1866</v>
+        <v>0.1884</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.034</v>
+        <v>-6.3039</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9536</v>
+        <v>-6.4756</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0804</v>
+        <v>0.1717</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.537</v>
+        <v>-6.5614</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.3198</v>
+        <v>-3.3501</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2172</v>
+        <v>-3.2114</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.9363</v>
+        <v>-3.9856</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.0353</v>
+        <v>-3.0766</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6007</v>
+        <v>-2.5758</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.3162</v>
+        <v>-2.3023</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6372</v>
+        <v>0.3957</v>
       </c>
       <c r="T11" t="n">
-        <v>1.476</v>
+        <v>0.0156</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1612</v>
+        <v>0.3801</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X11" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.2692</v>
+        <v>-7.6026</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7659</v>
+        <v>-3.099</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.5033</v>
+        <v>-4.5035</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.3624</v>
+        <v>-5.3701</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.5984</v>
+        <v>-2.621</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.764</v>
+        <v>-2.7492</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0204</v>
+        <v>-2.0509</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.6921</v>
+        <v>-2.7211</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.342</v>
+        <v>-3.3193</v>
       </c>
       <c r="N12" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.4357</v>
+        <v>-3.4194</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1859</v>
+        <v>-0.1429</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4548</v>
+        <v>0.1599</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2689</v>
+        <v>-0.3028</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.068199999999999</v>
+        <v>-8.6991</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0518</v>
+        <v>-4.3698</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.0164</v>
+        <v>-4.3293</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.1417</v>
+        <v>-6.1451</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0156</v>
+        <v>-2.0298</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.1261</v>
+        <v>-4.1153</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.7169</v>
+        <v>-2.7389</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.9679</v>
+        <v>-1.9865</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.4248</v>
+        <v>-3.4062</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.3771</v>
+        <v>-3.3629</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1267</v>
+        <v>0.238</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9739</v>
+        <v>-0.2652</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8471</v>
+        <v>0.5032</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-39.03939999999999</v>
+        <v>-38.7033</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.1886</v>
+        <v>-19.1579</v>
       </c>
       <c r="F14" t="n">
-        <v>-19.851</v>
+        <v>-19.5455</v>
       </c>
       <c r="G14" t="n">
-        <v>-37.399</v>
+        <v>-37.3971</v>
       </c>
       <c r="H14" t="n">
-        <v>-13.8367</v>
+        <v>-13.9249</v>
       </c>
       <c r="I14" t="n">
-        <v>-23.5625</v>
+        <v>-23.4724</v>
       </c>
       <c r="J14" t="n">
-        <v>-9.392400000000002</v>
+        <v>-9.639299999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.9374</v>
+        <v>-12.1243</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5451</v>
+        <v>2.485</v>
       </c>
       <c r="M14" t="n">
-        <v>-28.0067</v>
+        <v>-27.7578</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.899</v>
+        <v>-1.8004</v>
       </c>
       <c r="O14" t="n">
-        <v>-26.1074</v>
+        <v>-25.9572</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.999999999965592e-05</v>
+        <v>-9.99999999995449e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4758</v>
+        <v>-12.5198</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.8258</v>
+        <v>-3.4852</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.5231</v>
+        <v>-3.1633</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3026000000000002</v>
+        <v>-0.3215</v>
       </c>
       <c r="V14" t="n">
-        <v>2.185299999999999</v>
+        <v>2.179000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>6.2028</v>
+        <v>6.164800000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.0175</v>
+        <v>-3.9859</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.478999999999999</v>
+        <v>9.357100000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8951</v>
+        <v>5.8729</v>
       </c>
       <c r="F15" t="n">
-        <v>3.5839</v>
+        <v>3.4842</v>
       </c>
       <c r="G15" t="n">
-        <v>6.572</v>
+        <v>6.5733</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0113</v>
+        <v>2.0214</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5606</v>
+        <v>4.5519</v>
       </c>
       <c r="J15" t="n">
-        <v>5.185</v>
+        <v>5.166</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1949</v>
+        <v>1.1893</v>
       </c>
       <c r="L15" t="n">
-        <v>3.9902</v>
+        <v>3.9767</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3869</v>
+        <v>1.4073</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8165</v>
+        <v>0.832</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0658</v>
+        <v>0.9432</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2299</v>
+        <v>0.232</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8359</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.8809</v>
+        <v>7.3786</v>
       </c>
       <c r="E16" t="n">
-        <v>5.255</v>
+        <v>5.7819</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6259</v>
+        <v>1.5968</v>
       </c>
       <c r="G16" t="n">
-        <v>6.7437</v>
+        <v>6.7162</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1891</v>
+        <v>-0.1868</v>
       </c>
       <c r="I16" t="n">
-        <v>6.9328</v>
+        <v>6.9031</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2522</v>
+        <v>6.1956</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.7601</v>
+        <v>-1.7796</v>
       </c>
       <c r="L16" t="n">
-        <v>8.0123</v>
+        <v>7.9753</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4915</v>
+        <v>0.5206</v>
       </c>
       <c r="N16" t="n">
-        <v>1.571</v>
+        <v>1.5928</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7948</v>
+        <v>-0.2693</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9557</v>
+        <v>-0.3651</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1609</v>
+        <v>0.0958</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.3804</v>
+        <v>5.2722</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5455</v>
+        <v>1.9073</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8349</v>
+        <v>3.3649</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2921</v>
+        <v>5.28</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7445</v>
+        <v>1.7489</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5477</v>
+        <v>3.5311</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9052</v>
+        <v>3.8728</v>
       </c>
       <c r="K17" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9772</v>
+        <v>2.9559</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3869</v>
+        <v>1.4073</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8165</v>
+        <v>0.832</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8783</v>
+        <v>0.7921</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0162</v>
+        <v>0.4294</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1379</v>
+        <v>0.3627</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.9518</v>
+        <v>4.9375</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8956</v>
+        <v>3.4444</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0562</v>
+        <v>1.4932</v>
       </c>
       <c r="G18" t="n">
-        <v>6.6112</v>
+        <v>6.6064</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="I18" t="n">
-        <v>6.2665</v>
+        <v>6.2481</v>
       </c>
       <c r="J18" t="n">
-        <v>6.1196</v>
+        <v>6.0858</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2264</v>
+        <v>-1.2345</v>
       </c>
       <c r="L18" t="n">
-        <v>7.346</v>
+        <v>7.3203</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4915</v>
+        <v>0.5206</v>
       </c>
       <c r="N18" t="n">
-        <v>1.571</v>
+        <v>1.5928</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5252</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9557</v>
+        <v>-0.3651</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5695</v>
+        <v>-0.1656</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.5177</v>
+        <v>3.3422</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9964</v>
+        <v>2.0148</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5213</v>
+        <v>1.3274</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7239</v>
+        <v>3.3993</v>
       </c>
       <c r="H19" t="n">
-        <v>2.7057</v>
+        <v>3.5546</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0183</v>
+        <v>-0.1553</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4416</v>
+        <v>2.0758</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6207</v>
+        <v>1.6892</v>
       </c>
       <c r="L19" t="n">
-        <v>0.821</v>
+        <v>0.3866</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2823</v>
+        <v>1.3234</v>
       </c>
       <c r="N19" t="n">
-        <v>1.085</v>
+        <v>1.8653</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1973</v>
+        <v>-0.5419</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.2148</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2994</v>
+        <v>0.0575</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2655</v>
+        <v>-0.2724</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7712</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6105</v>
+        <v>1.2472</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.1567</v>
+        <v>3.2196</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4001</v>
+        <v>0.6175</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7566000000000001</v>
+        <v>2.6021</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3882</v>
+        <v>3.7194</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5349</v>
+        <v>2.6973</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1467</v>
+        <v>1.022</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0994</v>
+        <v>2.4255</v>
       </c>
       <c r="K20" t="n">
-        <v>1.697</v>
+        <v>1.6063</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4024</v>
+        <v>0.8192</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2888</v>
+        <v>1.2939</v>
       </c>
       <c r="N20" t="n">
-        <v>1.8379</v>
+        <v>1.0911</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.549</v>
+        <v>0.2028</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3923</v>
+        <v>0.2742</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4083</v>
+        <v>-0.0536</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8006</v>
+        <v>0.3278</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1607</v>
+        <v>-0.7739</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2534</v>
+        <v>-0.6162</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>3.0469</v>
+        <v>2.2636</v>
       </c>
       <c r="E21" t="n">
-        <v>3.3195</v>
+        <v>2.835</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2725</v>
+        <v>-0.5713</v>
       </c>
       <c r="G21" t="n">
-        <v>4.3784</v>
+        <v>4.3986</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6374</v>
+        <v>3.6552</v>
       </c>
       <c r="I21" t="n">
-        <v>0.741</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5614</v>
+        <v>3.5489</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9568</v>
+        <v>1.9478</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6046</v>
+        <v>1.6012</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8497</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6806</v>
+        <v>1.7074</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>1.4248</v>
+        <v>0.6099</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7561</v>
+        <v>0.2876</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6687</v>
+        <v>0.3223</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.6636</v>
+        <v>-3.6554</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>Z. HICKS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.3774</v>
+        <v>2.1149</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3767</v>
+        <v>1.0631</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0007</v>
+        <v>1.0519</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9575</v>
+        <v>1.6607</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8428</v>
+        <v>0.6629</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1147</v>
+        <v>0.9977</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8945</v>
+        <v>1.0562</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.4861</v>
+        <v>0.1034</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5917</v>
+        <v>0.9528</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.063</v>
+        <v>0.6044</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6433</v>
+        <v>0.5595</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7063</v>
+        <v>0.0449</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>1.4956</v>
+        <v>0.5634</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1785</v>
+        <v>0.0068</v>
       </c>
       <c r="U22" t="n">
-        <v>1.3171</v>
+        <v>0.5565</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9320000000000001</v>
+        <v>-1.2472</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Z. HICKS</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5279</v>
+        <v>1.6039</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7209</v>
+        <v>0.3577</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.2462</v>
       </c>
       <c r="G23" t="n">
-        <v>1.6584</v>
+        <v>-0.9528</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6535</v>
+        <v>-0.8334</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0048</v>
+        <v>-0.1194</v>
       </c>
       <c r="J23" t="n">
-        <v>1.0687</v>
+        <v>-0.9126</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1039</v>
+        <v>-1.4931</v>
       </c>
       <c r="L23" t="n">
-        <v>0.9648</v>
+        <v>0.5805</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5896</v>
+        <v>-0.0402</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5496</v>
+        <v>0.6597</v>
       </c>
       <c r="O23" t="n">
-        <v>0.04</v>
+        <v>-0.6998</v>
       </c>
       <c r="P23" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0112</v>
+        <v>0.7145</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3478</v>
+        <v>0.1808</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3366</v>
+        <v>0.5336</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2534</v>
+        <v>0.9317</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1.0554</v>
+        <v>1.1191</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8956</v>
+        <v>-3.3298</v>
       </c>
       <c r="F24" t="n">
-        <v>4.951</v>
+        <v>4.4489</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4344</v>
+        <v>1.4428</v>
       </c>
       <c r="H24" t="n">
-        <v>1.5784</v>
+        <v>1.5905</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.144</v>
+        <v>-0.1476</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5657</v>
+        <v>-0.5817</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7144</v>
+        <v>-0.7228</v>
       </c>
       <c r="M24" t="n">
-        <v>2.0001</v>
+        <v>2.0245</v>
       </c>
       <c r="N24" t="n">
-        <v>1.4297</v>
+        <v>1.4493</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5283</v>
+        <v>0.5867</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8347</v>
+        <v>-0.2442</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3631</v>
+        <v>0.831</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,40 +2359,40 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0367</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0322</v>
+        <v>-0.0325</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0378</v>
+        <v>-0.0042</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0213</v>
+        <v>-0.0193</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3359</v>
+        <v>-0.3351</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2404,13 +2404,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0487</v>
+        <v>-0.0174</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.2645</v>
+        <v>-1.5203</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.626</v>
+        <v>-0.9866</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6385</v>
+        <v>-0.5337</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.4246</v>
+        <v>-1.4275</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.6565</v>
+        <v>-1.6599</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2319</v>
+        <v>0.2324</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.2037</v>
+        <v>-1.2118</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.2783</v>
+        <v>-1.2863</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6403</v>
+        <v>0.382</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5777</v>
+        <v>0.2252</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0626</v>
+        <v>0.1568</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>39.03960000000001</v>
+        <v>39.0517</v>
       </c>
       <c r="E27" t="n">
-        <v>19.851</v>
+        <v>19.5457</v>
       </c>
       <c r="F27" t="n">
-        <v>19.1887</v>
+        <v>19.5064</v>
       </c>
       <c r="G27" t="n">
-        <v>37.3989</v>
+        <v>37.39709999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>13.8364</v>
+        <v>13.9249</v>
       </c>
       <c r="I27" t="n">
-        <v>23.5623</v>
+        <v>23.4723</v>
       </c>
       <c r="J27" t="n">
-        <v>28.0065</v>
+        <v>27.7577</v>
       </c>
       <c r="K27" t="n">
-        <v>1.8991</v>
+        <v>1.8004</v>
       </c>
       <c r="L27" t="n">
-        <v>26.10769999999999</v>
+        <v>25.9574</v>
       </c>
       <c r="M27" t="n">
-        <v>9.392099999999999</v>
+        <v>9.639300000000002</v>
       </c>
       <c r="N27" t="n">
-        <v>11.9375</v>
+        <v>12.1242</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.545</v>
+        <v>-2.485099999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>1.110223024625157e-16</v>
+        <v>1.942890293094024e-16</v>
       </c>
       <c r="Q27" t="n">
-        <v>-12.4758</v>
+        <v>-12.5197</v>
       </c>
       <c r="R27" t="n">
-        <v>12.4759</v>
+        <v>12.5199</v>
       </c>
       <c r="S27" t="n">
-        <v>3.8259</v>
+        <v>3.833800000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3026000000000001</v>
+        <v>0.3216000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>3.5233</v>
+        <v>3.512</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.1852</v>
+        <v>-2.178900000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>4.0176</v>
+        <v>3.9858</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.2028</v>
+        <v>-6.164800000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104522_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104522_W8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-3.9859</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104522_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.164800000000001</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
